--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -261,25 +261,40 @@
     <t>结束引导时的额外字段</t>
   </si>
   <si>
-    <t>第2关兑现引导</t>
-  </si>
-  <si>
-    <t>7,Plane/Plane1/BottomPart/WithdrawBtn/GuidePos</t>
-  </si>
-  <si>
-    <t>7,Plane/Plane1/BottomPart/WithdrawBtn</t>
-  </si>
-  <si>
-    <t>canWithdraw:1</t>
-  </si>
-  <si>
-    <t>第3关兑现引导</t>
-  </si>
-  <si>
-    <t>目标金额兑现引导</t>
-  </si>
-  <si>
-    <t>签到兑现引导</t>
+    <t>游玩引导1</t>
+  </si>
+  <si>
+    <t>4,Top/target_node/GuidePos1</t>
+  </si>
+  <si>
+    <t>4,Top/target_node/target_layout/target</t>
+  </si>
+  <si>
+    <t>4,</t>
+  </si>
+  <si>
+    <t>游玩引导2</t>
+  </si>
+  <si>
+    <t>4,Center/GuidePos3</t>
+  </si>
+  <si>
+    <t>4,Center/levelRoot</t>
+  </si>
+  <si>
+    <t>游玩引导3</t>
+  </si>
+  <si>
+    <t>4,Top/tmpNode/GuidePos2</t>
+  </si>
+  <si>
+    <t>4,Top/tmpNode/tmp_layout</t>
+  </si>
+  <si>
+    <t>游玩引导4</t>
+  </si>
+  <si>
+    <t>falseT:0</t>
   </si>
 </sst>
 </file>
@@ -687,9 +702,7 @@
       <right style="thin">
         <color theme="2"/>
       </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
@@ -702,7 +715,9 @@
       <right style="thin">
         <color theme="2"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
@@ -1546,6 +1561,9 @@
       <c r="B6">
         <v>10001</v>
       </c>
+      <c r="C6">
+        <v>10002</v>
+      </c>
       <c r="D6" s="5" t="s">
         <v>44</v>
       </c>
@@ -1559,12 +1577,15 @@
         <v>1</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>10089</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>45</v>
       </c>
+      <c r="L6" s="6"/>
       <c r="M6" t="b">
         <v>1</v>
       </c>
@@ -1572,21 +1593,22 @@
         <v>46</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q6" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" ht="27" spans="1:18">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7">
         <v>10002</v>
       </c>
+      <c r="C7">
+        <v>10003</v>
+      </c>
       <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E7">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1595,24 +1617,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6" t="s">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>10090</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="6"/>
       <c r="M7" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="Q7" s="6"/>
     </row>
     <row r="8" ht="27" spans="1:18">
       <c r="B8">
@@ -1622,10 +1645,10 @@
         <v>10004</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1634,31 +1657,38 @@
         <v>1</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6" t="s">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>10091</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="6"/>
       <c r="M8" t="b">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q8" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="Q8" s="6"/>
     </row>
     <row r="9" spans="1:18">
       <c r="B9">
         <v>10004</v>
       </c>
+      <c r="C9">
+        <v>10101</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E9">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1666,44 +1696,36 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" ht="27" spans="1:18">
-      <c r="B10">
-        <v>10005</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="J9">
+        <v>10092</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E10">
-        <v>10005</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q10" s="6" t="s">
+      <c r="O9" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="Q9" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="D10" s="7"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="D11" s="7"/>
+      <c r="D11" s="8"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="N11" s="6"/>
@@ -1711,7 +1733,7 @@
       <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="D12" s="8"/>
+      <c r="D12" s="7"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="N12" s="6"/>
@@ -1719,7 +1741,7 @@
       <c r="P12" s="6"/>
     </row>
     <row r="13" customFormat="1" spans="1:18">
-      <c r="D13" s="7"/>
+      <c r="D13" s="8"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1732,7 +1754,7 @@
       <c r="P13" s="6"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:18">
-      <c r="D14" s="8"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1745,7 +1767,7 @@
       <c r="P14" s="9"/>
     </row>
     <row r="15" customFormat="1" spans="1:18">
-      <c r="D15" s="7"/>
+      <c r="D15" s="8"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1757,7 +1779,7 @@
       <c r="P15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:18">
-      <c r="D16" s="7"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1782,7 +1804,7 @@
       <c r="P17" s="9"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="1"/>
@@ -1791,7 +1813,7 @@
       <c r="P18" s="9"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="7"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1804,7 +1826,7 @@
       <c r="P19" s="9"/>
     </row>
     <row r="20" spans="4:16">
-      <c r="D20" s="8"/>
+      <c r="D20" s="7"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="N20" s="6"/>
@@ -1812,7 +1834,7 @@
       <c r="P20" s="6"/>
     </row>
     <row r="21" spans="4:16">
-      <c r="D21" s="8"/>
+      <c r="D21" s="7"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="N21" s="6"/>
@@ -1836,7 +1858,7 @@
       <c r="P23" s="6"/>
     </row>
     <row r="24" spans="4:16">
-      <c r="D24" s="7"/>
+      <c r="D24" s="8"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="N24" s="6"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -264,37 +264,46 @@
     <t>游玩引导1</t>
   </si>
   <si>
-    <t>4,Top/target_node/GuidePos1</t>
-  </si>
-  <si>
-    <t>4,Top/target_node/target_layout/target</t>
-  </si>
-  <si>
-    <t>4,</t>
+    <t>2,Plane/Center/GuidePos</t>
+  </si>
+  <si>
+    <t>2,Plane/Center/CupPart/Bottle_0</t>
+  </si>
+  <si>
+    <t>handC:TRUE</t>
   </si>
   <si>
     <t>游玩引导2</t>
   </si>
   <si>
-    <t>4,Center/GuidePos3</t>
-  </si>
-  <si>
-    <t>4,Center/levelRoot</t>
+    <t>2,Plane/Center/CupPart/Bottle_1</t>
   </si>
   <si>
     <t>游玩引导3</t>
   </si>
   <si>
-    <t>4,Top/tmpNode/GuidePos2</t>
-  </si>
-  <si>
-    <t>4,Top/tmpNode/tmp_layout</t>
-  </si>
-  <si>
     <t>游玩引导4</t>
   </si>
   <si>
-    <t>falseT:0</t>
+    <t>handC:FALSE</t>
+  </si>
+  <si>
+    <t>兑现引导1</t>
+  </si>
+  <si>
+    <t>18,Plane/BottomPart/WithdrawBtn/GuidePos</t>
+  </si>
+  <si>
+    <t>18,Plane/BottomPart/WithdrawBtn</t>
+  </si>
+  <si>
+    <t>兑现引导2</t>
+  </si>
+  <si>
+    <t>兑现引导3</t>
+  </si>
+  <si>
+    <t>兑现引导4</t>
   </si>
 </sst>
 </file>
@@ -702,7 +711,9 @@
       <right style="thin">
         <color theme="2"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
@@ -715,9 +726,7 @@
       <right style="thin">
         <color theme="2"/>
       </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
@@ -1580,24 +1589,28 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>10089</v>
+        <v>10103</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="6"/>
+      <c r="L6" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="M6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="1:18">
+    </row>
+    <row r="7" ht="27" spans="1:18">
       <c r="B7">
         <v>10002</v>
       </c>
@@ -1620,24 +1633,26 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>10090</v>
+        <v>10104</v>
       </c>
       <c r="K7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="6"/>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" ht="27" spans="1:18">
+    <row r="8" spans="1:18">
       <c r="B8">
         <v>10003</v>
       </c>
@@ -1645,7 +1660,7 @@
         <v>10004</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>10001</v>
@@ -1659,22 +1674,21 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
       <c r="J8">
-        <v>10091</v>
+        <v>10105</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
     <row r="9" spans="1:18">
@@ -1682,10 +1696,10 @@
         <v>10004</v>
       </c>
       <c r="C9">
-        <v>10101</v>
+        <v>10005</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>10001</v>
@@ -1696,78 +1710,190 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
       <c r="J9">
-        <v>10092</v>
+        <v>10106</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="D10" s="7"/>
-      <c r="K10" s="6"/>
+      <c r="B10">
+        <v>10005</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>10001</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>10107</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="L10" s="6"/>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="D11" s="8"/>
+      <c r="R10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="27" spans="1:18">
+      <c r="B11">
+        <v>10006</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>10006</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="D12" s="7"/>
+    <row r="12" ht="27" spans="1:18">
+      <c r="B12">
+        <v>10007</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>10007</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" customFormat="1" spans="1:18">
-      <c r="D13" s="8"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
+    <row r="13" customFormat="1" ht="27" spans="1:18">
+      <c r="B13">
+        <v>10008</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13">
+        <v>10008</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
       <c r="H13"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:18">
-      <c r="D14" s="7"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+    <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
+      <c r="B14">
+        <v>10009</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14">
+        <v>10009</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="L14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="P14" s="9"/>
     </row>
     <row r="15" customFormat="1" spans="1:18">
-      <c r="D15" s="8"/>
+      <c r="D15" s="7"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1779,7 +1905,7 @@
       <c r="P15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:18">
-      <c r="D16" s="8"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1804,7 +1930,7 @@
       <c r="P17" s="9"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="8"/>
+      <c r="D18" s="7"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="1"/>
@@ -1813,7 +1939,7 @@
       <c r="P18" s="9"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="8"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1826,7 +1952,7 @@
       <c r="P19" s="9"/>
     </row>
     <row r="20" spans="4:16">
-      <c r="D20" s="7"/>
+      <c r="D20" s="8"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="N20" s="6"/>
@@ -1834,7 +1960,7 @@
       <c r="P20" s="6"/>
     </row>
     <row r="21" spans="4:16">
-      <c r="D21" s="7"/>
+      <c r="D21" s="8"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="N21" s="6"/>
@@ -1858,7 +1984,7 @@
       <c r="P23" s="6"/>
     </row>
     <row r="24" spans="4:16">
-      <c r="D24" s="8"/>
+      <c r="D24" s="7"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="N24" s="6"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -291,10 +291,10 @@
     <t>兑现引导1</t>
   </si>
   <si>
-    <t>18,Plane/BottomPart/WithdrawBtn/GuidePos</t>
-  </si>
-  <si>
-    <t>18,Plane/BottomPart/WithdrawBtn</t>
+    <t>18,Plane/Plane1/BottomPart/WithdrawBtn/GuidePos</t>
+  </si>
+  <si>
+    <t>18,Plane/Plane1/BottomPart/WithdrawBtn</t>
   </si>
   <si>
     <t>兑现引导2</t>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>18,Plane/Plane1/BottomPart/WithdrawBtn</t>
+  </si>
+  <si>
+    <t>canWithdraw:1</t>
   </si>
   <si>
     <t>兑现引导2</t>
@@ -1796,13 +1799,16 @@
         <v>13</v>
       </c>
       <c r="P11" s="6"/>
+      <c r="Q11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" ht="27" spans="1:18">
       <c r="B12">
         <v>10007</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>10007</v>
@@ -1827,13 +1833,16 @@
         <v>13</v>
       </c>
       <c r="P12" s="6"/>
+      <c r="Q12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="13" customFormat="1" ht="27" spans="1:18">
       <c r="B13">
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>10008</v>
@@ -1859,13 +1868,16 @@
         <v>13</v>
       </c>
       <c r="P13" s="6"/>
+      <c r="Q13" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
       <c r="B14">
         <v>10009</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>10009</v>
@@ -1891,6 +1903,9 @@
         <v>13</v>
       </c>
       <c r="P14" s="9"/>
+      <c r="Q14" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="15" customFormat="1" spans="1:18">
       <c r="D15" s="7"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>canWithdraw:1</t>
+  </si>
+  <si>
+    <t>iac:0</t>
   </si>
   <si>
     <t>兑现引导2</t>
@@ -1802,13 +1805,16 @@
       <c r="Q11" t="s">
         <v>56</v>
       </c>
+      <c r="R11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="12" ht="27" spans="1:18">
       <c r="B12">
         <v>10007</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>10007</v>
@@ -1836,13 +1842,16 @@
       <c r="Q12" t="s">
         <v>56</v>
       </c>
+      <c r="R12" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="13" customFormat="1" ht="27" spans="1:18">
       <c r="B13">
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>10008</v>
@@ -1871,13 +1880,16 @@
       <c r="Q13" t="s">
         <v>56</v>
       </c>
+      <c r="R13" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
       <c r="B14">
         <v>10009</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>10009</v>
@@ -1905,6 +1917,9 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:18">

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -297,16 +297,22 @@
     <t>18,Plane/Plane1/BottomPart/WithdrawBtn</t>
   </si>
   <si>
+    <t>canWithdraw:1,</t>
+  </si>
+  <si>
+    <t>iac:0</t>
+  </si>
+  <si>
+    <t>兑现引导2</t>
+  </si>
+  <si>
     <t>canWithdraw:1</t>
   </si>
   <si>
-    <t>iac:0</t>
-  </si>
-  <si>
-    <t>兑现引导2</t>
-  </si>
-  <si>
     <t>兑现引导3</t>
+  </si>
+  <si>
+    <t>canWithdraw:1;iac:0</t>
   </si>
   <si>
     <t>兑现引导4</t>
@@ -1840,7 +1846,7 @@
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R12" t="s">
         <v>57</v>
@@ -1851,7 +1857,7 @@
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>10008</v>
@@ -1860,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13"/>
       <c r="K13" s="6"/>
@@ -1878,10 +1884,7 @@
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" t="s">
-        <v>56</v>
-      </c>
-      <c r="R13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
@@ -1889,7 +1892,7 @@
         <v>10009</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>10009</v>
@@ -1916,7 +1919,7 @@
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>57</v>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1687,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J8">
         <v>10105</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="L8" s="6"/>
       <c r="M8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J9">
         <v>10106</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="L9" s="6"/>
       <c r="M9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J10">
         <v>10107</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="L10" s="6"/>
       <c r="M10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -277,45 +277,6 @@
   </si>
   <si>
     <t>2,Plane/Center/CupPart/Bottle_1</t>
-  </si>
-  <si>
-    <t>游玩引导3</t>
-  </si>
-  <si>
-    <t>游玩引导4</t>
-  </si>
-  <si>
-    <t>handC:FALSE</t>
-  </si>
-  <si>
-    <t>兑现引导1</t>
-  </si>
-  <si>
-    <t>18,Plane/Plane1/BottomPart/WithdrawBtn/GuidePos</t>
-  </si>
-  <si>
-    <t>18,Plane/Plane1/BottomPart/WithdrawBtn</t>
-  </si>
-  <si>
-    <t>canWithdraw:1,</t>
-  </si>
-  <si>
-    <t>iac:0</t>
-  </si>
-  <si>
-    <t>兑现引导2</t>
-  </si>
-  <si>
-    <t>canWithdraw:1</t>
-  </si>
-  <si>
-    <t>兑现引导3</t>
-  </si>
-  <si>
-    <t>canWithdraw:1;iac:0</t>
-  </si>
-  <si>
-    <t>兑现引导4</t>
   </si>
 </sst>
 </file>
@@ -1626,9 +1587,7 @@
       <c r="B7">
         <v>10002</v>
       </c>
-      <c r="C7">
-        <v>10003</v>
-      </c>
+      <c r="C7"/>
       <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
@@ -1665,265 +1624,97 @@
       <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="B8">
-        <v>10003</v>
-      </c>
-      <c r="C8">
-        <v>10004</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>10001</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1.5</v>
-      </c>
-      <c r="J8">
-        <v>10105</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>45</v>
-      </c>
+      <c r="D8" s="5"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
+      <c r="M8"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="B9">
-        <v>10004</v>
-      </c>
-      <c r="C9">
-        <v>10005</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9">
-        <v>10001</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1.5</v>
-      </c>
-      <c r="J9">
-        <v>10106</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>45</v>
-      </c>
+      <c r="D9" s="5"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
+      <c r="M9"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="B10">
-        <v>10005</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10">
-        <v>10001</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1.5</v>
-      </c>
-      <c r="J10">
-        <v>10107</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>45</v>
-      </c>
+      <c r="D10" s="5"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
+      <c r="M10"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
-      <c r="R10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:18">
-      <c r="B11">
-        <v>10006</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11">
-        <v>10006</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="D11" s="7"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
       <c r="K11" s="6"/>
-      <c r="L11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L11" s="6"/>
+      <c r="M11"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
       <c r="P11" s="6"/>
-      <c r="Q11" t="s">
-        <v>56</v>
-      </c>
-      <c r="R11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:18">
-      <c r="B12">
-        <v>10007</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12">
-        <v>10007</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="D12" s="8"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
       <c r="K12" s="6"/>
-      <c r="L12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L12" s="6"/>
+      <c r="M12"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
       <c r="P12" s="6"/>
-      <c r="Q12" t="s">
-        <v>59</v>
-      </c>
-      <c r="R12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="27" spans="1:18">
-      <c r="B13">
-        <v>10008</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13">
-        <v>10008</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:18">
+      <c r="D13" s="7"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
       <c r="H13"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L13" s="6"/>
+      <c r="M13"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
       <c r="P13" s="6"/>
-      <c r="Q13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
-      <c r="B14">
-        <v>10009</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>10009</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:18">
+      <c r="B14"/>
+      <c r="D14" s="8"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
       <c r="H14" s="1"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L14" s="6"/>
+      <c r="M14"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
       <c r="P14" s="9"/>
-      <c r="Q14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="15" customFormat="1" spans="1:18">
       <c r="D15" s="7"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1539,7 +1537,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:18">
+    <row r="6" customFormat="1" ht="27" spans="1:18">
       <c r="B6">
         <v>10001</v>
       </c>
@@ -1583,11 +1581,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:18">
+    <row r="7" customFormat="1" ht="27" spans="1:18">
       <c r="B7">
         <v>10002</v>
       </c>
-      <c r="C7"/>
       <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
@@ -1625,66 +1622,40 @@
     </row>
     <row r="8" spans="1:18">
       <c r="D8" s="5"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
     <row r="9" spans="1:18">
       <c r="D9" s="5"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-      <c r="M9"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="1:18">
       <c r="D10" s="5"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:18">
       <c r="D11" s="7"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-      <c r="M11"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:18">
       <c r="D12" s="8"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
-      <c r="M12"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
@@ -1821,28 +1792,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -275,6 +275,15 @@
   </si>
   <si>
     <t>2,Plane/Center/CupPart/Bottle_1</t>
+  </si>
+  <si>
+    <t>游玩引导3</t>
+  </si>
+  <si>
+    <t>游玩引导4</t>
+  </si>
+  <si>
+    <t>handC:FALSE</t>
   </si>
 </sst>
 </file>
@@ -1585,6 +1594,9 @@
       <c r="B7">
         <v>10002</v>
       </c>
+      <c r="C7">
+        <v>10003</v>
+      </c>
       <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
@@ -1620,29 +1632,119 @@
       </c>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:18">
-      <c r="D8" s="5"/>
-      <c r="K8" s="6"/>
+    <row r="8" customFormat="1" spans="1:18">
+      <c r="B8">
+        <v>10003</v>
+      </c>
+      <c r="C8">
+        <v>10004</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>10001</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1.5</v>
+      </c>
+      <c r="J8">
+        <v>10105</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="L8" s="6"/>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="D9" s="5"/>
-      <c r="K9" s="6"/>
+    <row r="9" customFormat="1" spans="1:18">
+      <c r="B9">
+        <v>10004</v>
+      </c>
+      <c r="C9">
+        <v>10005</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>10001</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1.5</v>
+      </c>
+      <c r="J9">
+        <v>10106</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="L9" s="6"/>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:18">
-      <c r="D10" s="5"/>
-      <c r="K10" s="6"/>
+    <row r="10" customFormat="1" spans="1:18">
+      <c r="B10">
+        <v>10005</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>10001</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1.5</v>
+      </c>
+      <c r="J10">
+        <v>10107</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="L10" s="6"/>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
+      <c r="R10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="11" spans="1:18">
       <c r="D11" s="7"/>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1610,7 +1610,7 @@
         <v>46</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>46</v>
@@ -1618,6 +1618,7 @@
       <c r="O6" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="P6"/>
       <c r="Q6" s="6" t="s">
         <v>47</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>49</v>
@@ -1662,6 +1663,7 @@
       <c r="O7" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="P7"/>
       <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:18">

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -1578,7 +1578,7 @@
         <v>46</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>46</v>
@@ -1622,7 +1622,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>49</v>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -1618,7 +1618,6 @@
       <c r="O6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P6"/>
       <c r="Q6" s="6" t="s">
         <v>47</v>
       </c>
@@ -1663,7 +1662,6 @@
       <c r="O7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P7"/>
       <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:18">
@@ -1801,7 +1799,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>55</v>
@@ -1838,7 +1836,7 @@
         <v>54</v>
       </c>
       <c r="M12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>55</v>
@@ -1876,7 +1874,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>55</v>
@@ -1911,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>55</v>

--- a/DesignerConfigs/Datas/Guides.xlsx
+++ b/DesignerConfigs/Datas/Guides.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -286,36 +286,6 @@
   </si>
   <si>
     <t>handC:FALSE</t>
-  </si>
-  <si>
-    <t>兑现引导1</t>
-  </si>
-  <si>
-    <t>18,Plane/Plane1/BottomPart/WithdrawBtn/GuidePos</t>
-  </si>
-  <si>
-    <t>18,Plane/Plane1/BottomPart/WithdrawBtn</t>
-  </si>
-  <si>
-    <t>canWithdraw:1,</t>
-  </si>
-  <si>
-    <t>iac:0</t>
-  </si>
-  <si>
-    <t>兑现引导2</t>
-  </si>
-  <si>
-    <t>canWithdraw:1</t>
-  </si>
-  <si>
-    <t>兑现引导3</t>
-  </si>
-  <si>
-    <t>canWithdraw:1;iac:0</t>
-  </si>
-  <si>
-    <t>兑现引导4</t>
   </si>
 </sst>
 </file>
@@ -1778,152 +1748,56 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:18">
-      <c r="B11">
-        <v>10006</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11">
-        <v>10006</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
+    <row r="11" spans="1:18">
+      <c r="D11" s="7"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
       <c r="K11" s="6"/>
-      <c r="L11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L11" s="6"/>
+      <c r="M11"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
       <c r="P11" s="6"/>
-      <c r="Q11" t="s">
-        <v>56</v>
-      </c>
-      <c r="R11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:18">
-      <c r="B12">
-        <v>10007</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12">
-        <v>10007</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="D12" s="8"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
       <c r="K12" s="6"/>
-      <c r="L12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L12" s="6"/>
+      <c r="M12"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
       <c r="P12" s="6"/>
-      <c r="Q12" t="s">
-        <v>59</v>
-      </c>
-      <c r="R12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="27" spans="1:18">
-      <c r="B13">
-        <v>10008</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13">
-        <v>10008</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:18">
+      <c r="D13" s="7"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
       <c r="H13"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L13" s="6"/>
+      <c r="M13"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
       <c r="P13" s="6"/>
-      <c r="Q13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:18">
-      <c r="B14">
-        <v>10009</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>10009</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:18">
+      <c r="B14"/>
+      <c r="D14" s="8"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
       <c r="H14" s="1"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="L14" s="6"/>
+      <c r="M14"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
       <c r="P14" s="9"/>
-      <c r="Q14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="15" customFormat="1" spans="1:18">
       <c r="D15" s="7"/>
